--- a/media/exports/reports/2026-08/program-cost.xlsx
+++ b/media/exports/reports/2026-08/program-cost.xlsx
@@ -24,45 +24,54 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -95,35 +104,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -939,8 +948,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1645,8 +1654,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1922,8 +1931,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/program-cost.xlsx
+++ b/media/exports/reports/2026-08/program-cost.xlsx
@@ -12,7 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$9:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -210,6 +213,155 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Full cost of each program, August 2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>$</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="#,##0;(#,##0)"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$10:$A$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$10:$B$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="program_cost_Data" displayName="program_cost_Data" ref="A9:F15" headerRowCount="1">
+  <autoFilter ref="A9:F15"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Program"/>
+    <tableColumn id="2" name="Grant spending, Aug 2026"/>
+    <tableColumn id="3" name="Share"/>
+    <tableColumn id="4" name="Untied costs share"/>
+    <tableColumn id="5" name="Administration share"/>
+    <tableColumn id="6" name="Full cost"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -520,14 +672,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -658,43 +810,13 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Housing support is the biggest program: $53,592 in August once its share of untied program costs and administration is added to $30,500 of grant spending. Shared costs add 75.7% on top of grant spending across all programs.</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19"/>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Program: Housing support</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -705,7 +827,7 @@
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Housing support cost $53,592 in full in August: $30,500 paid by the State Housing Program grant, and $23,092 of shared costs no grant covers. It has spent 94.4% of its budget to date, with $133,500 left and 4 months to go.</t>
+          <t>Housing support is the biggest program: $53,592 in August once its share of untied program costs and administration is added to $30,500 of grant spending. Shared costs add 75.7% on top of grant spending across all programs.</t>
         </is>
       </c>
     </row>
@@ -720,7 +842,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $53,592 a month; $23,092 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
         </is>
       </c>
     </row>
@@ -728,7 +850,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Program: Youth outreach</t>
+          <t>Program: Housing support</t>
         </is>
       </c>
     </row>
@@ -742,7 +864,7 @@
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Youth outreach cost $37,778 in full in August: $21,500 paid by the State Department of Families grant, and $16,278 of shared costs no grant covers. It has spent 101.2% of its budget to date, with $196,500 left and 10 months to go.</t>
+          <t>Housing support cost $53,592 in full in August: $30,500 paid by the State Housing Program grant, and $23,092 of shared costs no grant covers. It has spent 94.4% of its budget to date, with $133,500 left and 4 months to go.</t>
         </is>
       </c>
     </row>
@@ -757,7 +879,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $37,778 a month; $16,278 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost is $53,592 a month; $23,092 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
@@ -765,7 +887,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Program: Mental health first aid</t>
+          <t>Program: Youth outreach</t>
         </is>
       </c>
     </row>
@@ -779,7 +901,7 @@
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Mental health first aid cost $16,517 in full in August: $9,400 paid by the Federal health program grant, and $7,117 of shared costs no grant covers. It has spent 92.8% of its budget to date, with $73,600 left and 7 months to go.</t>
+          <t>Youth outreach cost $37,778 in full in August: $21,500 paid by the State Department of Families grant, and $16,278 of shared costs no grant covers. It has spent 101.2% of its budget to date, with $196,500 left and 10 months to go.</t>
         </is>
       </c>
     </row>
@@ -794,7 +916,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $16,517 a month; $7,117 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost is $37,778 a month; $16,278 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
@@ -802,7 +924,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Program: Digital literacy</t>
+          <t>Program: Mental health first aid</t>
         </is>
       </c>
     </row>
@@ -816,7 +938,7 @@
     <row r="46" ht="45" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Digital literacy cost $9,137 in full in August: $5,200 paid by the Philanthropic foundation grant, and $3,937 of shared costs no grant covers. It has spent 99.5% of its budget to date, with $35,300 left and 7 months to go.</t>
+          <t>Mental health first aid cost $16,517 in full in August: $9,400 paid by the Federal health program grant, and $7,117 of shared costs no grant covers. It has spent 92.8% of its budget to date, with $73,600 left and 7 months to go.</t>
         </is>
       </c>
     </row>
@@ -831,7 +953,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $9,137 a month; $3,937 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost is $16,517 a month; $7,117 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
@@ -839,7 +961,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Program: Community meals</t>
+          <t>Program: Digital literacy</t>
         </is>
       </c>
     </row>
@@ -853,7 +975,7 @@
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Community meals cost $7,204 in full in August: $4,100 paid by the Local council community grant grant, and $3,104 of shared costs no grant covers. It has spent 96.2% of its budget to date, with $40,300 left and 10 months to go.</t>
+          <t>Digital literacy cost $9,137 in full in August: $5,200 paid by the Philanthropic foundation grant, and $3,937 of shared costs no grant covers. It has spent 99.5% of its budget to date, with $35,300 left and 7 months to go.</t>
         </is>
       </c>
     </row>
@@ -868,7 +990,7 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $7,204 a month; $3,104 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost is $9,137 a month; $3,937 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
@@ -876,7 +998,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Program: Volunteer coordinator</t>
+          <t>Program: Community meals</t>
         </is>
       </c>
     </row>
@@ -890,7 +1012,7 @@
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Volunteer coordinator cost $5,271 in full in August: $3,000 paid by the State volunteering grant grant, and $2,271 of shared costs no grant covers. It has spent 100.0% of its budget to date, with $18,000 left and 6 months to go.</t>
+          <t>Community meals cost $7,204 in full in August: $4,100 paid by the Local council community grant grant, and $3,104 of shared costs no grant covers. It has spent 96.2% of its budget to date, with $40,300 left and 10 months to go.</t>
         </is>
       </c>
     </row>
@@ -905,7 +1027,7 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>The full cost is $5,271 a month; $2,271 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+          <t>The full cost is $7,204 a month; $3,104 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
@@ -913,30 +1035,67 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
+          <t>Program: Volunteer coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Volunteer coordinator cost $5,271 in full in August: $3,000 paid by the State volunteering grant grant, and $2,271 of shared costs no grant covers. It has spent 100.0% of its budget to date, with $18,000 left and 6 months to go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>The full cost is $5,271 a month; $2,271 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
           <t>Every program at once</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>Grant spending, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
+    <row r="74"/>
+    <row r="75"/>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A49:D49"/>
@@ -949,7 +1108,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -958,8 +1117,9 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="23" min="0" max="16383" man="1"/>
     <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="64" min="0" max="16383" man="1"/>
+    <brk id="65" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -988,14 +1148,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1815,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1695,14 +1855,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1932,11 +2092,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-08/program-cost.xlsx
+++ b/media/exports/reports/2026-08/program-cost.xlsx
@@ -679,7 +679,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Youth outreach cost $37,778 in full in August: $21,500 paid by the State Department of Families grant, and $16,278 of shared costs no grant covers. It has spent 101.2% of its budget to date, with $196,500 left and 10 months to go.</t>
+          <t>Youth outreach cost $37,778 in full in August: $21,500 paid by the State Department of Families grant, and $16,278 of shared costs no grant covers. It has spent 101.3% of its budget to date, with $196,500 left and 10 months to go.</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Community meals cost $7,204 in full in August: $4,100 paid by the Local council community grant grant, and $3,104 of shared costs no grant covers. It has spent 96.2% of its budget to date, with $40,300 left and 10 months to go.</t>
+          <t>Community meals cost $7,204 in full in August: $4,100 paid by the Local council community grant grant, and $3,104 of shared costs no grant covers. It has spent 96.3% of its budget to date, with $40,300 left and 10 months to go.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1155,7 +1155,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1862,7 +1862,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/program-cost.xlsx
+++ b/media/exports/reports/2026-08/program-cost.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$74</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$9:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$15</definedName>
@@ -51,13 +51,13 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
-      <sz val="12"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -109,15 +109,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -279,12 +282,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$10:$A$15</f>
+              <f>'Report'!$A$11:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$10:$B$15</f>
+              <f>'Report'!$B$11:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -328,7 +331,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2340000"/>
@@ -653,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -679,7 +682,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -687,129 +690,135 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Housing support costs $53,592 in full in August: $23,092 more than its grant spending, once its share of shared costs is added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Each program's full cost: what its grant pays for, plus its fair share of the costs no single grant covers (untied program costs and administration, shared by grant spending). Pick a program and every chart and note follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Program: All programs</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Program: All programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Full cost of each program, August 2026</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>% of total</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>Workings!B15</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
-        <f>Workings!B10</f>
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B11" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>Workings!B23</f>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>Workings!B15</f>
+        <v/>
+      </c>
+      <c r="C11" s="10">
+        <f>Workings!B10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Workings!B41</f>
-        <v/>
-      </c>
-      <c r="C12" s="9">
-        <f>Workings!B36</f>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>Workings!B23</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Digital literacy</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-      <c r="C13" s="9">
-        <f>Workings!B49</f>
+          <t>Mental health first aid</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>Workings!B41</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>Workings!B36</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="B14" s="8">
-        <f>Workings!B67</f>
-        <v/>
-      </c>
-      <c r="C14" s="9">
-        <f>Workings!B62</f>
+          <t>Digital literacy</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>Workings!B54</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>Workings!B49</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Community meals</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>Workings!B67</f>
+        <v/>
+      </c>
+      <c r="C15" s="10">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B16" s="9">
         <f>Workings!B80</f>
         <v/>
       </c>
-      <c r="C15" s="9">
+      <c r="C16" s="10">
         <f>Workings!B75</f>
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
@@ -817,307 +826,309 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Housing support is the biggest program: $53,592 in August once its share of untied program costs and administration is added to $30,500 of grant spending. Shared costs add 75.7% on top of grant spending across all programs.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Program: Housing support</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Housing support cost $53,592 in full in August: $30,500 paid by the State Housing Program grant, and $23,092 of shared costs no grant covers. It has spent 94.4% of its budget to date, with $133,500 left and 4 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>The full cost is $53,592 a month; $23,092 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Program: Youth outreach</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Youth outreach cost $37,778 in full in August: $21,500 paid by the State Department of Families grant, and $16,278 of shared costs no grant covers. It has spent 101.3% of its budget to date, with $196,500 left and 10 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>The full cost is $37,778 a month; $16,278 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Program: Mental health first aid</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Mental health first aid cost $16,517 in full in August: $9,400 paid by the Federal health program grant, and $7,117 of shared costs no grant covers. It has spent 92.8% of its budget to date, with $73,600 left and 7 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>The full cost is $16,517 a month; $7,117 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Program: Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Digital literacy cost $9,137 in full in August: $5,200 paid by the Philanthropic foundation grant, and $3,937 of shared costs no grant covers. It has spent 99.5% of its budget to date, with $35,300 left and 7 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>The full cost is $9,137 a month; $3,937 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Program: Community meals</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Community meals cost $7,204 in full in August: $4,100 paid by the Local council community grant grant, and $3,104 of shared costs no grant covers. It has spent 96.3% of its budget to date, with $40,300 left and 10 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>The full cost is $7,204 a month; $3,104 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Program: Volunteer coordinator</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Volunteer coordinator cost $5,271 in full in August: $3,000 paid by the State volunteering grant grant, and $2,271 of shared costs no grant covers. It has spent 100.0% of its budget to date, with $18,000 left and 6 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>The full cost is $5,271 a month; $2,271 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Every program at once</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Grant spending, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75"/>
+    <row r="76"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="23" min="0" max="16383" man="1"/>
-    <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="65" min="0" max="16383" man="1"/>
+    <brk id="24" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="66" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1155,28 +1166,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Housing support: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1188,7 +1199,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>30500</v>
       </c>
     </row>
@@ -1198,7 +1209,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1208,7 +1219,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <f>B8/B9</f>
         <v/>
       </c>
@@ -1219,7 +1230,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1229,7 +1240,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>B10*B11</f>
         <v/>
       </c>
@@ -1240,7 +1251,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1250,18 +1261,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>B10*B13</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="16">
         <f>B8+B12+B14</f>
         <v/>
       </c>
@@ -1269,22 +1280,22 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Youth outreach: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1296,7 +1307,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -1306,7 +1317,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1316,7 +1327,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <f>B21/B22</f>
         <v/>
       </c>
@@ -1327,7 +1338,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1337,7 +1348,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="13">
         <f>B23*B24</f>
         <v/>
       </c>
@@ -1348,7 +1359,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1358,18 +1369,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="13">
         <f>B23*B26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="16">
         <f>B21+B25+B27</f>
         <v/>
       </c>
@@ -1377,22 +1388,22 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Mental health first aid: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1404,7 +1415,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>9400</v>
       </c>
     </row>
@@ -1414,7 +1425,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1424,7 +1435,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1435,7 +1446,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1445,7 +1456,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="13">
         <f>B36*B37</f>
         <v/>
       </c>
@@ -1456,7 +1467,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1466,18 +1477,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="13">
         <f>B36*B39</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="16">
         <f>B34+B38+B40</f>
         <v/>
       </c>
@@ -1485,22 +1496,22 @@
     <row r="42"/>
     <row r="43"/>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Digital literacy: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1512,7 +1523,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>5200</v>
       </c>
     </row>
@@ -1522,7 +1533,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1532,7 +1543,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47/B48</f>
         <v/>
       </c>
@@ -1543,7 +1554,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1553,7 +1564,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="13">
         <f>B49*B50</f>
         <v/>
       </c>
@@ -1564,7 +1575,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1574,18 +1585,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="13">
         <f>B49*B52</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="16">
         <f>B47+B51+B53</f>
         <v/>
       </c>
@@ -1593,22 +1604,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Community meals: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1620,7 +1631,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="13" t="n">
         <v>4100</v>
       </c>
     </row>
@@ -1630,7 +1641,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1640,7 +1651,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60/B61</f>
         <v/>
       </c>
@@ -1651,7 +1662,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n">
+      <c r="B63" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1661,7 +1672,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="13">
         <f>B62*B63</f>
         <v/>
       </c>
@@ -1672,7 +1683,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1682,18 +1693,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="13">
         <f>B62*B65</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="16">
         <f>B60+B64+B66</f>
         <v/>
       </c>
@@ -1701,22 +1712,22 @@
     <row r="68"/>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Volunteer coordinator: full cost, August</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr"/>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr"/>
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Aug 2026</t>
         </is>
@@ -1728,7 +1739,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="13" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -1738,7 +1749,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n">
+      <c r="B74" s="13" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1748,7 +1759,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="14">
         <f>B73/B74</f>
         <v/>
       </c>
@@ -1759,7 +1770,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B76" s="13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1769,7 +1780,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="13">
         <f>B75*B76</f>
         <v/>
       </c>
@@ -1780,7 +1791,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="n">
+      <c r="B78" s="13" t="n">
         <v>36300</v>
       </c>
     </row>
@@ -1790,18 +1801,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="13">
         <f>B75*B78</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="14" t="inlineStr">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B80" s="15">
+      <c r="B80" s="16">
         <f>B73+B77+B79</f>
         <v/>
       </c>
@@ -1815,7 +1826,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1862,7 +1873,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1884,7 @@
           <t>All grant-funded program spending, August 2026</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>73700</v>
       </c>
     </row>
@@ -1883,7 +1894,7 @@
           <t>Untied program costs, August 2026 (all programs)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1893,195 +1904,195 @@
           <t>Administration, August 2026 (all)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>36300</v>
       </c>
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Grant spending, Aug 2026</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Untied costs share</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Administration share</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Full cost</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>30500</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>B10/$B$5</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>C10*$B$6</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>C10*$B$7</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>B10+D10+E10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>21500</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <f>B11/$B$5</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>C11*$B$6</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>C11*$B$7</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>B11+D11+E11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>9400</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>B12/$B$5</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="13">
         <f>C12*$B$6</f>
         <v/>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <f>C12*$B$7</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>B12+D12+E12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>5200</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <f>B13/$B$5</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>C13*$B$6</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>C13*$B$7</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>B13+D13+E13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>4100</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <f>B14/$B$5</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>C14*$B$6</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>C14*$B$7</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>B14+D14+E14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>3000</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="14">
         <f>B15/$B$5</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="13">
         <f>C15*$B$6</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <f>C15*$B$7</f>
         <v/>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>B15+D15+E15</f>
         <v/>
       </c>
@@ -2092,7 +2103,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
